--- a/public/templates/staff_upload_template.xlsx
+++ b/public/templates/staff_upload_template.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild=""/>
+  <fileVersion appName="Polaris Office Sheet" lastEdited="7" lowestEdited="7" rupBuild=""/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="229">
   <si>
     <t>email</t>
   </si>
@@ -27,103 +27,680 @@
     <t>full_name</t>
   </si>
   <si>
-    <t>role</t>
-  </si>
-  <si>
     <t>department_code</t>
   </si>
   <si>
     <t>department_name</t>
   </si>
   <si>
-    <t>position</t>
-  </si>
-  <si>
-    <t>user1@example.com</t>
-  </si>
-  <si>
-    <t>Temp1234!</t>
-  </si>
-  <si>
-    <t>홍길동</t>
+    <t>필드</t>
+  </si>
+  <si>
+    <t>필수</t>
+  </si>
+  <si>
+    <t>설명</t>
+  </si>
+  <si>
+    <t>로그인 이메일 (중복 시 건너뜀)</t>
+  </si>
+  <si>
+    <t>임시 비밀번호 (6자 이상)</t>
+  </si>
+  <si>
+    <t>선택</t>
+  </si>
+  <si>
+    <t>이름</t>
+  </si>
+  <si>
+    <t>부서/지점 코드 (코드가 우선 적용됨)</t>
+  </si>
+  <si>
+    <t>부서/지점 이름 (코드가 없을 때 매칭)</t>
+  </si>
+  <si>
+    <t>role1</t>
+  </si>
+  <si>
+    <t>role2</t>
+  </si>
+  <si>
+    <t>Learning Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Leader </t>
+  </si>
+  <si>
+    <t>student / admin (기본: student)</t>
+  </si>
+  <si>
+    <t>chanki.jeon@nonfiction.com</t>
+  </si>
+  <si>
+    <t>nonfiction1</t>
+  </si>
+  <si>
+    <t>전찬기</t>
   </si>
   <si>
     <t>student</t>
   </si>
-  <si>
-    <t>HQ</t>
-  </si>
-  <si>
-    <t>본사</t>
-  </si>
-  <si>
-    <t>사원</t>
-  </si>
-  <si>
-    <t>teacher1@example.com</t>
-  </si>
-  <si>
-    <t>김강사</t>
-  </si>
-  <si>
-    <t>teacher</t>
-  </si>
-  <si>
-    <t>교육팀</t>
-  </si>
-  <si>
-    <t>강사</t>
-  </si>
-  <si>
-    <t>필드</t>
-  </si>
-  <si>
-    <t>필수</t>
-  </si>
-  <si>
-    <t>설명</t>
-  </si>
-  <si>
-    <t>로그인 이메일 (중복 시 건너뜀)</t>
-  </si>
-  <si>
-    <t>임시 비밀번호 (6자 이상)</t>
-  </si>
-  <si>
-    <t>선택</t>
-  </si>
-  <si>
-    <t>이름</t>
-  </si>
-  <si>
-    <t>student / teacher / admin (기본: student)</t>
-  </si>
-  <si>
-    <t>부서/지점 코드 (코드가 우선 적용됨)</t>
-  </si>
-  <si>
-    <t>부서/지점 이름 (코드가 없을 때 매칭)</t>
-  </si>
-  <si>
-    <t>직급</t>
-  </si>
-  <si>
-    <t>test@nonfiction.com</t>
-  </si>
-  <si>
-    <t>temp1234!</t>
-  </si>
-  <si>
-    <t>role1</t>
-  </si>
-  <si>
-    <t>role2</t>
-  </si>
-  <si>
-    <t>learning leader</t>
-  </si>
-  <si>
-    <t>Learning Leader</t>
+  <si/>
+  <si>
+    <t>스타필드 수원</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>dahwon.kim@nonfiction.com</t>
+  </si>
+  <si>
+    <t>김다훤</t>
+  </si>
+  <si>
+    <t>성수</t>
+  </si>
+  <si>
+    <t>gaeul.kim@nonfiction.com</t>
+  </si>
+  <si>
+    <t>김가을</t>
+  </si>
+  <si>
+    <t>신사</t>
+  </si>
+  <si>
+    <t>jaeho.shin@nonfiction.com</t>
+  </si>
+  <si>
+    <t>신재호</t>
+  </si>
+  <si>
+    <t>롯데월드몰</t>
+  </si>
+  <si>
+    <t>jeonghee.lee@nonfiction.com</t>
+  </si>
+  <si>
+    <t>이정희</t>
+  </si>
+  <si>
+    <t>jiheon.kim@nonfiction.com</t>
+  </si>
+  <si>
+    <t>김지헌</t>
+  </si>
+  <si>
+    <t>jiwon.choi@nonfiction.com</t>
+  </si>
+  <si>
+    <t>최지원</t>
+  </si>
+  <si>
+    <t>한남</t>
+  </si>
+  <si>
+    <t>jonghyeok.park@nonfiction.com</t>
+  </si>
+  <si>
+    <t>박종혁</t>
+  </si>
+  <si>
+    <t>soyeong.park@nonfiction.com</t>
+  </si>
+  <si>
+    <t>박소영</t>
+  </si>
+  <si>
+    <t>yeji.kim@nonfiction.com</t>
+  </si>
+  <si>
+    <t>김예지</t>
+  </si>
+  <si>
+    <t>yena970723@gmail.com</t>
+  </si>
+  <si>
+    <t>송예나</t>
+  </si>
+  <si>
+    <t>삼청</t>
+  </si>
+  <si>
+    <t>haechan.han@nonfiction.com</t>
+  </si>
+  <si>
+    <t>한해찬</t>
+  </si>
+  <si>
+    <t>heeyeon.lee@nonfiction.com</t>
+  </si>
+  <si>
+    <t>이희연</t>
+  </si>
+  <si>
+    <t>kyeongyeon.kim@nonfiction.com</t>
+  </si>
+  <si>
+    <t>김경연</t>
+  </si>
+  <si>
+    <t>chaerin.lee@nonfiction.com</t>
+  </si>
+  <si>
+    <t>이채린</t>
+  </si>
+  <si>
+    <t>jihyeon.yeon@nonfiction.com</t>
+  </si>
+  <si>
+    <t>연지현</t>
+  </si>
+  <si>
+    <t>jina.lim@nonfiction.com</t>
+  </si>
+  <si>
+    <t>임진아</t>
+  </si>
+  <si>
+    <t>juyeon.kim@nonfiction.com</t>
+  </si>
+  <si>
+    <t>김주연</t>
+  </si>
+  <si>
+    <t>yeji.park@nonfiction.com</t>
+  </si>
+  <si>
+    <t>박예지</t>
+  </si>
+  <si>
+    <t>hwee.namkung@nonfiction.com</t>
+  </si>
+  <si>
+    <t>남궁휘</t>
+  </si>
+  <si>
+    <t>juhee.yoo@nonfiction.com</t>
+  </si>
+  <si>
+    <t>유주희</t>
+  </si>
+  <si>
+    <t>lan.cui@nonfiction.com</t>
+  </si>
+  <si>
+    <t>CUILAN</t>
+  </si>
+  <si>
+    <t>롯데면세점 본점</t>
+  </si>
+  <si>
+    <t>mihyang.kim@nonfiction.com</t>
+  </si>
+  <si>
+    <t>김미향</t>
+  </si>
+  <si>
+    <t>miyeon.yim@nonfiction.com</t>
+  </si>
+  <si>
+    <t>임미연</t>
+  </si>
+  <si>
+    <t>jiyeaon.nam@nonfiction.com</t>
+  </si>
+  <si>
+    <t>남지연</t>
+  </si>
+  <si>
+    <t>seunghyeon.lee@nonfiction.com</t>
+  </si>
+  <si>
+    <t>이승현</t>
+  </si>
+  <si>
+    <t>suryeon.heo@nonfiction.com</t>
+  </si>
+  <si>
+    <t>허수련</t>
+  </si>
+  <si>
+    <t>youkyung.kim@nonfiction.com</t>
+  </si>
+  <si>
+    <t>김유경</t>
+  </si>
+  <si>
+    <t>eunji.lee@nonfiction.com</t>
+  </si>
+  <si>
+    <t>이은지</t>
+  </si>
+  <si>
+    <t>minhee.yu@nonfiction.com</t>
+  </si>
+  <si>
+    <t>유민희</t>
+  </si>
+  <si>
+    <t>xumei.yu@nonfiction.com</t>
+  </si>
+  <si>
+    <t>유설매</t>
+  </si>
+  <si>
+    <t>yerin.woo@nonfiction.com</t>
+  </si>
+  <si>
+    <t>우예린</t>
+  </si>
+  <si>
+    <t>hyewon.kang@nonfiction.com</t>
+  </si>
+  <si>
+    <t>강혜원</t>
+  </si>
+  <si>
+    <t>제주신라</t>
+  </si>
+  <si>
+    <t>jihee.hyun@nonfiction.com</t>
+  </si>
+  <si>
+    <t>현지희</t>
+  </si>
+  <si>
+    <t>jihyun.jeong@nonfiction.com</t>
+  </si>
+  <si>
+    <t>정지현</t>
+  </si>
+  <si>
+    <t>juchan.kang@nonfiction.com</t>
+  </si>
+  <si>
+    <t>강주찬</t>
+  </si>
+  <si>
+    <t>yunju.jeong@nonfiction.com</t>
+  </si>
+  <si>
+    <t>정윤주</t>
+  </si>
+  <si>
+    <t>ama.ho@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Ama Ho</t>
+  </si>
+  <si>
+    <t>Hollywood</t>
+  </si>
+  <si>
+    <t>HK</t>
+  </si>
+  <si>
+    <t>chiho.wakai@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Chiho Yamashita</t>
+  </si>
+  <si>
+    <t>Daikanyama</t>
+  </si>
+  <si>
+    <t>JP</t>
+  </si>
+  <si>
+    <t>hui_eunice@yahoo.com</t>
+  </si>
+  <si>
+    <t>Eunice Hui</t>
+  </si>
+  <si>
+    <t>kimmysit@yahoo.com.hk</t>
+  </si>
+  <si>
+    <t>Kimmy Sit</t>
+  </si>
+  <si>
+    <t>kurumi.takahashi@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Kurumi Takahashi</t>
+  </si>
+  <si>
+    <t>misuzu.mogi@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Mogi Misuzu</t>
+  </si>
+  <si>
+    <t>Office</t>
+  </si>
+  <si>
+    <t>moe.yokota@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Moe Yokota</t>
+  </si>
+  <si>
+    <t>urara.taguchi@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Urara Taguchi</t>
+  </si>
+  <si>
+    <t>rin.iwasawa@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Rin Iwasawa</t>
+  </si>
+  <si>
+    <t>Hankyu</t>
+  </si>
+  <si>
+    <t>kanako.tsukai@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Kanako Tsukai</t>
+  </si>
+  <si>
+    <t>nanami.kidosaki@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Nanami Kidosaki</t>
+  </si>
+  <si>
+    <t>karin.fukuda@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Karin Fukuda</t>
+  </si>
+  <si>
+    <t>minji.kim@nonfiction.com</t>
+  </si>
+  <si>
+    <t>김민지</t>
+  </si>
+  <si>
+    <t>heejeong.seo@nonfiction.com</t>
+  </si>
+  <si>
+    <t>서희정</t>
+  </si>
+  <si>
+    <t>ayako.horiguchi@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Ayako Horiguchi</t>
+  </si>
+  <si>
+    <t>Hankyu / Kobe BAL</t>
+  </si>
+  <si>
+    <t>chaeyeon.park@nonfiction.com</t>
+  </si>
+  <si>
+    <t>박채연</t>
+  </si>
+  <si>
+    <t>chiaki.kuroda@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Chiaki Kuroda</t>
+  </si>
+  <si>
+    <t>Kobe BAL</t>
+  </si>
+  <si>
+    <t>miyu.suzuki@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Miyu Suzuki</t>
+  </si>
+  <si>
+    <t>takeo.yamamoto@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Takeo Yamamoto</t>
+  </si>
+  <si>
+    <t>sojung.park@nonfiction.com</t>
+  </si>
+  <si>
+    <t>박소정</t>
+  </si>
+  <si>
+    <t>seungbyi2.kim@nonfiction.com</t>
+  </si>
+  <si>
+    <t>김승비</t>
+  </si>
+  <si>
+    <t>chiyun.lu@nonfiction.com</t>
+  </si>
+  <si>
+    <t>여기운</t>
+  </si>
+  <si>
+    <t>ryanghee.kim@nonfiction.com</t>
+  </si>
+  <si>
+    <t>김량희</t>
+  </si>
+  <si>
+    <t>kakuko.kiyota@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Kakuko Kiyota</t>
+  </si>
+  <si>
+    <t>kana.sawada@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Kana Sawada</t>
+  </si>
+  <si>
+    <t>Daikanyama</t>
+  </si>
+  <si>
+    <t>rui.nakashima@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Rui Nakashima</t>
+  </si>
+  <si>
+    <t>saki.horiguchi@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Saki Horiguchi</t>
+  </si>
+  <si>
+    <t>gaeun.kim@nonfiction.com</t>
+  </si>
+  <si>
+    <t>김가은</t>
+  </si>
+  <si>
+    <t>gijun.nam@nonfiction.com</t>
+  </si>
+  <si>
+    <t>남기준</t>
+  </si>
+  <si>
+    <t>yaeri.kang@nonfiction.com</t>
+  </si>
+  <si>
+    <t>강예리</t>
+  </si>
+  <si>
+    <t>cx@nonfiction.com</t>
+  </si>
+  <si>
+    <t>CXTeam</t>
+  </si>
+  <si>
+    <t>nayeon.kim@nonfiction.com</t>
+  </si>
+  <si>
+    <t>김나연</t>
+  </si>
+  <si>
+    <t>akane.ogino@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Akane Ogino</t>
+  </si>
+  <si>
+    <t>rion.sakaguchi@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Rion Sakaguchi</t>
+  </si>
+  <si>
+    <t>charles.harley@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Charles Harley</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>hollywoodroadhk@nonfiction.com</t>
+  </si>
+  <si>
+    <t>HK Store</t>
+  </si>
+  <si>
+    <t>mason.reed@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Mason Reed</t>
+  </si>
+  <si>
+    <t>matteo.diaz-miranda@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Matteo Diaz-Miranda</t>
+  </si>
+  <si>
+    <t>zachary.ceniceros@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Zachary Ceniceros</t>
+  </si>
+  <si>
+    <t>chenghuan.an@nonfiction.com</t>
+  </si>
+  <si>
+    <t>안성환</t>
+  </si>
+  <si>
+    <t>somi.kang@nonfiction.com</t>
+  </si>
+  <si>
+    <t>강소미</t>
+  </si>
+  <si>
+    <t>sunggon.lee@nonfiction.com</t>
+  </si>
+  <si>
+    <t>이성곤</t>
+  </si>
+  <si>
+    <t>mi.her@nonfiction.com</t>
+  </si>
+  <si>
+    <t>허미</t>
+  </si>
+  <si>
+    <t>yeongseong.lee@nonfiction.com</t>
+  </si>
+  <si>
+    <t>이영성</t>
+  </si>
+  <si>
+    <t>mina.jeong@nonfiction.com</t>
+  </si>
+  <si>
+    <t>정미나</t>
+  </si>
+  <si>
+    <t>kanako.otani@nonfiction.com</t>
+  </si>
+  <si>
+    <t>Kanako Otani</t>
+  </si>
+  <si>
+    <t>LTWM</t>
+  </si>
+  <si>
+    <t>HN</t>
+  </si>
+  <si>
+    <t>SW</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>센텀</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>LTDF</t>
+  </si>
+  <si>
+    <t>인천공항 T1</t>
+  </si>
+  <si>
+    <t>인천공항 T2</t>
+  </si>
+  <si>
+    <t>ICN T1</t>
+  </si>
+  <si>
+    <t>ICN T2</t>
+  </si>
+  <si>
+    <t>JJ</t>
+  </si>
+  <si>
+    <t>DK</t>
+  </si>
+  <si>
+    <t>HW</t>
+  </si>
+  <si>
+    <t>OFC</t>
+  </si>
+  <si>
+    <t>HK</t>
+  </si>
+  <si>
+    <t>KB</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>SN</t>
+  </si>
+  <si>
+    <t>region</t>
   </si>
 </sst>
 </file>
@@ -131,7 +708,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="12.0"/>
       <name val="맑은 고딕"/>
@@ -151,6 +728,26 @@
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
       <color theme="11"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="10"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF0611F2"/>
+    </font>
+    <font>
+      <sz val="8.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -263,20 +860,14 @@
       <color rgb="FF7F7F7F"/>
     </font>
     <font>
-      <u/>
-      <sz val="12.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="10"/>
-    </font>
-    <font>
+      <b/>
       <sz val="12.0"/>
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
       <color theme="1"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -472,6 +1063,18 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0611F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -588,10 +1191,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -607,193 +1219,207 @@
     <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
-    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
-    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
-    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
-    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
-    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
-    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
-    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
-    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
-    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
-    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
-    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
-    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
-    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
-    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
-    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
-    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
-    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
-    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
-    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
-    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
-    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
-    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
-    <cellStyle name="경고문" xfId="9" builtinId="11"/>
-    <cellStyle name="계산" xfId="17" builtinId="22"/>
-    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
-    <cellStyle name="메모" xfId="8" builtinId="10"/>
-    <cellStyle name="백분율" xfId="3" builtinId="5"/>
-    <cellStyle name="보통" xfId="23" builtinId="28"/>
-    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
-    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="쉼표[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
-    <cellStyle name="열어본 하이퍼링크" xfId="7" builtinId="9" hidden="1"/>
-    <cellStyle name="요약" xfId="20" builtinId="25"/>
-    <cellStyle name="입력" xfId="15" builtinId="20"/>
-    <cellStyle name="제목" xfId="10" builtinId="15"/>
-    <cellStyle name="제목1" xfId="11" builtinId="16"/>
-    <cellStyle name="제목2" xfId="12" builtinId="17"/>
-    <cellStyle name="제목3" xfId="13" builtinId="18"/>
-    <cellStyle name="제목4" xfId="14" builtinId="19"/>
-    <cellStyle name="좋음" xfId="21" builtinId="26"/>
-    <cellStyle name="출력" xfId="16" builtinId="21"/>
-    <cellStyle name="통화" xfId="2" builtinId="4"/>
-    <cellStyle name="통화[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="하이퍼링크" xfId="6" builtinId="8" hidden="1"/>
+    <cellStyle name="20% - 강조색1" xfId="26" builtinId="30"/>
+    <cellStyle name="20% - 강조색2" xfId="30" builtinId="34"/>
+    <cellStyle name="20% - 강조색3" xfId="34" builtinId="38"/>
+    <cellStyle name="20% - 강조색4" xfId="38" builtinId="42"/>
+    <cellStyle name="20% - 강조색5" xfId="42" builtinId="46"/>
+    <cellStyle name="20% - 강조색6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 강조색1" xfId="27" builtinId="31"/>
+    <cellStyle name="40% - 강조색2" xfId="31" builtinId="35"/>
+    <cellStyle name="40% - 강조색3" xfId="35" builtinId="39"/>
+    <cellStyle name="40% - 강조색4" xfId="39" builtinId="43"/>
+    <cellStyle name="40% - 강조색5" xfId="43" builtinId="47"/>
+    <cellStyle name="40% - 강조색6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 강조색1" xfId="28" builtinId="32"/>
+    <cellStyle name="60% - 강조색2" xfId="32" builtinId="36"/>
+    <cellStyle name="60% - 강조색3" xfId="36" builtinId="40"/>
+    <cellStyle name="60% - 강조색4" xfId="40" builtinId="44"/>
+    <cellStyle name="60% - 강조색5" xfId="44" builtinId="48"/>
+    <cellStyle name="60% - 강조색6" xfId="48" builtinId="52"/>
+    <cellStyle name="강조색1" xfId="25" builtinId="29"/>
+    <cellStyle name="강조색2" xfId="29" builtinId="33"/>
+    <cellStyle name="강조색3" xfId="33" builtinId="37"/>
+    <cellStyle name="강조색4" xfId="37" builtinId="41"/>
+    <cellStyle name="강조색5" xfId="41" builtinId="45"/>
+    <cellStyle name="강조색6" xfId="45" builtinId="49"/>
+    <cellStyle name="경고문" xfId="10" builtinId="11"/>
+    <cellStyle name="계산" xfId="18" builtinId="22"/>
+    <cellStyle name="나쁨" xfId="23" builtinId="27"/>
+    <cellStyle name="메모" xfId="9" builtinId="10"/>
+    <cellStyle name="백분율" xfId="6" builtinId="5"/>
+    <cellStyle name="보통" xfId="24" builtinId="28"/>
+    <cellStyle name="설명텍스트" xfId="49" builtinId="53"/>
+    <cellStyle name="셀 확인" xfId="19" builtinId="23"/>
+    <cellStyle name="쉼표" xfId="4" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="7" builtinId="6"/>
+    <cellStyle name="연결된 셀" xfId="20" builtinId="24"/>
+    <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="요약" xfId="21" builtinId="25"/>
+    <cellStyle name="입력" xfId="16" builtinId="20"/>
+    <cellStyle name="제목" xfId="11" builtinId="15"/>
+    <cellStyle name="제목1" xfId="12" builtinId="16"/>
+    <cellStyle name="제목2" xfId="13" builtinId="17"/>
+    <cellStyle name="제목3" xfId="14" builtinId="18"/>
+    <cellStyle name="제목4" xfId="15" builtinId="19"/>
+    <cellStyle name="좋음" xfId="22" builtinId="26"/>
+    <cellStyle name="출력" xfId="17" builtinId="21"/>
+    <cellStyle name="통화" xfId="5" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="8" builtinId="7"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
   </cellStyles>
 </styleSheet>
 </file>
@@ -1120,51 +1746,2205 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15.000000"/>
+  <dimension ref="A1:H84"/>
+  <sheetFormatPr defaultRowHeight="17.250000"/>
   <cols>
-    <col min="1" max="1" width="24.78277800" customWidth="1" outlineLevel="0"/>
-    <col min="2" max="3" width="14.78277800" customWidth="1" outlineLevel="0"/>
-    <col min="4" max="4" width="15.56055567" customWidth="1" outlineLevel="0"/>
-    <col min="5" max="5" width="16.22722265" customWidth="1" outlineLevel="0"/>
+    <col min="1" max="1" style="2" width="35.44944594" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="3" style="2" width="14.78277800" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="4" style="2" width="15.56055567" customWidth="1" outlineLevel="0"/>
+    <col min="5" max="5" style="2" width="16.22722265" customWidth="1" outlineLevel="0"/>
+    <col min="6" max="6" style="2" width="17.56055472" customWidth="1" outlineLevel="0"/>
+    <col min="7" max="7" style="2" width="19.33833334" customWidth="1" outlineLevel="0"/>
+    <col min="8" max="8" style="2" width="18.11611197" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.250000">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="17.250000">
-      <c r="A2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="D5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>35</v>
+      <c r="H6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="A84"/>
+  </hyperlinks>
   <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -1173,7 +3953,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15.000000"/>
+  <sheetFormatPr defaultRowHeight="17.250000"/>
   <cols>
     <col min="1" max="1" width="18.78277800" customWidth="1" outlineLevel="0"/>
     <col min="2" max="2" width="8.78277800" customWidth="1" outlineLevel="0"/>
@@ -1182,13 +3962,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="0" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1196,10 +3976,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1207,10 +3987,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1218,54 +3998,54 @@
         <v>2</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="0" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="0" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="0" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>24</v>
-      </c>
       <c r="C8" s="0" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
